--- a/public/templates/octa-invoice-quote-template.xlsx
+++ b/public/templates/octa-invoice-quote-template.xlsx
@@ -75,7 +75,7 @@
     <t>LINE TOTAL</t>
   </si>
   <si>
-    <t>e.g. OCTA-X Ethanol 96% - 25L plastic drum</t>
+    <t>e.g. OCTA-X Plus Ethanol 96% - 25L</t>
   </si>
   <si>
     <t>No VAT charged: the supplier is not registered for VAT.</t>

--- a/public/templates/octa-invoice-quote-template.xlsx
+++ b/public/templates/octa-invoice-quote-template.xlsx
@@ -75,7 +75,7 @@
     <t>LINE TOTAL</t>
   </si>
   <si>
-    <t>e.g. OCTA-X Plus Ethanol 96% - 25L</t>
+    <t>e.g. OCTA-X Ethanol 95% - 25L</t>
   </si>
   <si>
     <t>No VAT charged: the supplier is not registered for VAT.</t>
